--- a/Week 3/ten_tips_for_charts.xlsx
+++ b/Week 3/ten_tips_for_charts.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E8A3DDB-4D9C-4155-9C4F-40088254241A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{1E8A3DDB-4D9C-4155-9C4F-40088254241A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98EE3A4B-5164-40D9-8282-255C386014E6}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="10" xr2:uid="{53C78ED7-DDA0-4AE4-BCF6-674254D8C7B1}"/>
+    <workbookView xWindow="2630" yWindow="1750" windowWidth="19570" windowHeight="12620" activeTab="3" xr2:uid="{53C78ED7-DDA0-4AE4-BCF6-674254D8C7B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Start" sheetId="2" r:id="rId1"/>
@@ -454,7 +454,14 @@
     <cellStyle name="Title 2" xfId="3" xr:uid="{7CFBCD2A-9F84-449D-B456-22B4A1CFB6F6}"/>
     <cellStyle name="z A Column text" xfId="7" xr:uid="{8335E534-3B51-4BEF-8D04-F835BAC8E001}"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -509,8 +516,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="CustomTableStyle" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -33243,7 +33250,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2CF44F44-6583-4ED5-A449-4119FF501C34}" name="RecommendedChartData" displayName="RecommendedChartData" ref="B12:C16" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6E1FC270-3EE1-4FF1-8490-B832AF259C7D}" name="Salesperson"/>
-    <tableColumn id="2" xr3:uid="{ABD5AAA2-5FC1-42C3-88E8-54DF572DDBA7}" name="Amount sold" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{ABD5AAA2-5FC1-42C3-88E8-54DF572DDBA7}" name="Amount sold" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="CustomTableStyle" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -33258,8 +33265,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{27414BAC-ACF8-43CE-A8CA-F68415D658EC}" name="RecommendedChartData3" displayName="RecommendedChartData3" ref="B12:D16" totalsRowShown="0">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{762FF5D1-22CC-4505-A7A7-4539A3917FDC}" name="Salesperson"/>
-    <tableColumn id="2" xr3:uid="{C606BD3E-9325-476A-A5AD-7C813C477619}" name="Sales" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{60151564-2A79-402B-81CE-765C4A7EDE57}" name="Commission" dataDxfId="8" dataCellStyle="Normal 2">
+    <tableColumn id="2" xr3:uid="{C606BD3E-9325-476A-A5AD-7C813C477619}" name="Sales" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{60151564-2A79-402B-81CE-765C4A7EDE57}" name="Commission" dataDxfId="9" dataCellStyle="Normal 2">
       <calculatedColumnFormula>0.05*RecommendedChartData3[[#This Row],[Sales]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -33273,6 +33280,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{FC29282E-3538-4A5A-8318-830915ABDD1F}" name="Table9" displayName="Table9" ref="C13:E16" totalsRowShown="0" headerRowBorderDxfId="0" dataCellStyle="Normal 5 2 2">
+  <autoFilter ref="C13:E16" xr:uid="{FC29282E-3538-4A5A-8318-830915ABDD1F}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{577A268C-F931-41D8-B1EC-BB34D6F26232}" name="Salesperson" dataCellStyle="Normal 5 2 2"/>
+    <tableColumn id="2" xr3:uid="{3D7EEC25-9CE1-4853-A8D8-5EBA7549A76E}" name="Jan" dataCellStyle="Normal 5 2 2"/>
+    <tableColumn id="3" xr3:uid="{EE3C0985-D35C-4061-994C-7BF8CB06B140}" name="Feb" dataCellStyle="Normal 5 2 2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CE5ECD12-E99C-41D4-837D-31C85FE31A2E}" name="Table4" displayName="Table4" ref="C100:G105" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{BBCCB46F-1EDC-4311-A169-F0B553C173DD}" name="Salesperson"/>
@@ -33285,51 +33304,51 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CF3102AB-6169-42B0-B1C1-FAE990390C09}" name="tbl_pvtchrts" displayName="tbl_pvtchrts" ref="B13:C18" totalsRowShown="0">
   <autoFilter ref="B13:C18" xr:uid="{00000000-0009-0000-0100-000016000000}"/>
   <tableColumns count="2">
     <tableColumn id="2" xr3:uid="{874FDDCF-88F0-4DAA-A944-4D7168F383B0}" name="Product"/>
-    <tableColumn id="3" xr3:uid="{4CA54BFE-906D-4799-84EB-56A147451722}" name="Amount" dataDxfId="7"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A57D7224-3185-4ABB-A928-42872ECBD348}" name="tbl_secondaryaxis15" displayName="tbl_secondaryaxis15" ref="G12:I18" totalsRowShown="0">
-  <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{B499664A-B19C-4D2D-889C-FA866087B7A8}" name="Date" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{FB3FAF6C-C2EC-4CBD-8CFF-3DA5CB505E01}" name="Sales" dataDxfId="5" dataCellStyle="Normal 2"/>
-    <tableColumn id="3" xr3:uid="{2A29CC9F-1389-4B6B-B07F-EEE50C5EADE9}" name="Profit %" dataDxfId="4" dataCellStyle="Normal 5 2 2"/>
+    <tableColumn id="3" xr3:uid="{4CA54BFE-906D-4799-84EB-56A147451722}" name="Amount" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A710BA4D-1C5C-4222-9C55-A031C171F343}" name="tbl_secondaryaxis6" displayName="tbl_secondaryaxis6" ref="G13:I18" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A57D7224-3185-4ABB-A928-42872ECBD348}" name="tbl_secondaryaxis15" displayName="tbl_secondaryaxis15" ref="G12:I18" totalsRowShown="0">
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{82F72803-F37D-4392-AAC3-7C9CBC06B121}" name="Date" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{95020895-E079-4468-B59B-182899290B02}" name="Attendance" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{7BBA4995-0C2A-4D9E-98FA-EA30461ABA39}" name="Food sales" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{B499664A-B19C-4D2D-889C-FA866087B7A8}" name="Date" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{FB3FAF6C-C2EC-4CBD-8CFF-3DA5CB505E01}" name="Sales" dataDxfId="6" dataCellStyle="Normal 2"/>
+    <tableColumn id="3" xr3:uid="{2A29CC9F-1389-4B6B-B07F-EEE50C5EADE9}" name="Profit %" dataDxfId="5" dataCellStyle="Normal 5 2 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B200C274-2CCC-470E-B929-4418797DF727}" name="Table192122242526" displayName="Table192122242526" ref="F12:G18" totalsRowShown="0">
-  <autoFilter ref="F12:G18" xr:uid="{00000000-0009-0000-0100-000019000000}"/>
-  <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{97132582-3AD4-47A1-AF80-7692FC4E4093}" name="Product"/>
-    <tableColumn id="3" xr3:uid="{A130EAA5-A2DE-40E8-A3F9-71B78958BBF5}" name="Amount" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A710BA4D-1C5C-4222-9C55-A031C171F343}" name="tbl_secondaryaxis6" displayName="tbl_secondaryaxis6" ref="G13:I18" totalsRowShown="0">
+  <tableColumns count="3">
+    <tableColumn id="2" xr3:uid="{82F72803-F37D-4392-AAC3-7C9CBC06B121}" name="Date" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{95020895-E079-4468-B59B-182899290B02}" name="Attendance" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{7BBA4995-0C2A-4D9E-98FA-EA30461ABA39}" name="Food sales" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B200C274-2CCC-470E-B929-4418797DF727}" name="Table192122242526" displayName="Table192122242526" ref="F12:G18" totalsRowShown="0">
+  <autoFilter ref="F12:G18" xr:uid="{00000000-0009-0000-0100-000019000000}"/>
+  <tableColumns count="2">
+    <tableColumn id="2" xr3:uid="{97132582-3AD4-47A1-AF80-7692FC4E4093}" name="Product"/>
+    <tableColumn id="3" xr3:uid="{A130EAA5-A2DE-40E8-A3F9-71B78958BBF5}" name="Amount" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{2D798D39-5D74-4174-A3A9-D60539BA7907}" name="Table410" displayName="Table410" ref="B100:F103" totalsRowShown="0">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{CC3A817C-01C3-43A5-97DF-FCF465001BCD}" name="Salesperson"/>
@@ -33644,29 +33663,29 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="11.109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.08984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="115.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="11.109375" style="2"/>
+    <col min="1" max="1" width="115.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.54296875" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="11.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="63" x14ac:dyDescent="1.3">
+    <row r="2" spans="1:1" ht="61.5" x14ac:dyDescent="1.45">
       <c r="A2" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="44.4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" ht="44" x14ac:dyDescent="0.5">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="200.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" ht="200.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
     </row>
   </sheetData>
@@ -33683,42 +33702,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6686533-C7FE-4B60-A7F0-CB6411E26A69}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="3" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.08984375" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F12" s="11" t="s">
         <v>16</v>
       </c>
@@ -33726,7 +33745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F13" s="12" t="s">
         <v>18</v>
       </c>
@@ -33734,7 +33753,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F14" s="12" t="s">
         <v>31</v>
       </c>
@@ -33742,7 +33761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F15" s="12" t="s">
         <v>32</v>
       </c>
@@ -33750,7 +33769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F16" s="12" t="s">
         <v>33</v>
       </c>
@@ -33758,7 +33777,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F17" s="12" t="s">
         <v>19</v>
       </c>
@@ -33766,7 +33785,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="6:7" x14ac:dyDescent="0.35">
       <c r="F18" s="12" t="s">
         <v>34</v>
       </c>
@@ -33774,57 +33793,57 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.35">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
       <c r="L107" s="25"/>
@@ -33848,46 +33867,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D78B336-BF6D-4771-B5CD-EE5F7BCB6FCC}">
   <sheetPr codeName="Sheet12"/>
   <dimension ref="A1:M110"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="3" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.08984375" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L11" s="10"/>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B100" s="11" t="s">
         <v>2</v>
       </c>
@@ -33904,7 +33923,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B101" s="11" t="s">
         <v>4</v>
       </c>
@@ -33921,7 +33940,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B102" s="11" t="s">
         <v>5</v>
       </c>
@@ -33938,7 +33957,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B103" s="11" t="s">
         <v>6</v>
       </c>
@@ -33955,7 +33974,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
@@ -33963,29 +33982,29 @@
       <c r="L104" s="11"/>
       <c r="M104" s="11"/>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.35">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
       <c r="L105" s="11"/>
       <c r="M105" s="11"/>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.35">
       <c r="L106" s="11"/>
       <c r="M106" s="11"/>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.35">
       <c r="L107" s="11"/>
       <c r="M107" s="11"/>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.35">
       <c r="L108" s="11"/>
       <c r="M108" s="11"/>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.35">
       <c r="L109" s="11"/>
       <c r="M109" s="11"/>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.35">
       <c r="L110" s="11"/>
       <c r="M110" s="11"/>
     </row>
@@ -34015,30 +34034,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:B6"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.7" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="6"/>
-    <col min="2" max="2" width="95.109375" style="11" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="11"/>
+    <col min="1" max="1" width="8.90625" style="6"/>
+    <col min="2" max="2" width="95.08984375" style="11" customWidth="1"/>
+    <col min="3" max="16384" width="8.90625" style="11"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" s="36" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" s="36" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
       <c r="B2" s="11"/>
     </row>
-    <row r="3" spans="1:2" s="36" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" s="36" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6"/>
       <c r="B3" s="11"/>
     </row>
-    <row r="4" spans="1:2" s="37" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" s="37" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A4" s="21"/>
       <c r="B4" s="11"/>
     </row>
-    <row r="5" spans="1:2" s="38" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" s="38" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="B5" s="11"/>
     </row>
-    <row r="6" spans="1:2" s="38" customFormat="1" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" s="38" customFormat="1" ht="14.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="B6" s="11"/>
     </row>
@@ -34063,46 +34082,46 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E7193D5-8253-4A58-B990-AD52407E3E4A}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="3" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.08984375" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="9"/>
       <c r="L9" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"Good job! You placed"," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"your first column field."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L11" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"Click Next to continue..."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B12" s="11" t="s">
         <v>2</v>
       </c>
@@ -34110,7 +34129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B13" s="12" t="s">
         <v>4</v>
       </c>
@@ -34118,7 +34137,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B14" s="12" t="s">
         <v>5</v>
       </c>
@@ -34126,7 +34145,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B15" s="12" t="s">
         <v>6</v>
       </c>
@@ -34134,7 +34153,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
@@ -34142,60 +34161,60 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="15"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34222,45 +34241,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{558CDC37-9CD8-48D1-939D-AFCE43F83555}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="2" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="2" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="11.08984375" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"Good job! You placed"," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"your first column field."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L11" s="10" t="str">
         <f>IF(AND($B$14="Buyer",$I$18=1175),"Click Next to continue..."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B12" s="11" t="s">
         <v>2</v>
       </c>
@@ -34271,7 +34290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B13" s="12" t="s">
         <v>4</v>
       </c>
@@ -34283,7 +34302,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B14" s="12" t="s">
         <v>5</v>
       </c>
@@ -34295,7 +34314,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B15" s="12" t="s">
         <v>6</v>
       </c>
@@ -34307,7 +34326,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
@@ -34319,57 +34338,57 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34395,57 +34414,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA3EC7F-66B1-4143-BE9F-A02A63FC9037}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="2" width="4.109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" style="7" customWidth="1"/>
-    <col min="5" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="2" width="4.08984375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="8.08984375" style="7" customWidth="1"/>
+    <col min="5" max="9" width="11.08984375" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8"/>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8"/>
     </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" s="10" t="str">
         <f>IF(AND($C$15="Buyer",$I$18=1175),"Good job! You placed"," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10" t="str">
         <f>IF(AND($C$15="Buyer",$I$18=1175),"your first column field."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="K11" s="10" t="str">
         <f>IF(AND($C$15="Buyer",$I$18=1175),"Click Next to continue..."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C13" s="18" t="s">
         <v>2</v>
       </c>
@@ -34456,7 +34475,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C14" s="11" t="s">
         <v>4</v>
       </c>
@@ -34467,7 +34486,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C15" s="11" t="s">
         <v>5</v>
       </c>
@@ -34478,7 +34497,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C16" s="11" t="s">
         <v>6</v>
       </c>
@@ -34489,62 +34508,62 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:5" x14ac:dyDescent="0.35">
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34560,6 +34579,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -34567,66 +34589,66 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A9FCD3-95CA-48E4-B341-6706423068E4}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:O107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="2" width="4.109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" style="7" customWidth="1"/>
-    <col min="5" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="2" width="4.08984375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="8.08984375" style="7" customWidth="1"/>
+    <col min="5" max="9" width="11.08984375" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O3" s="20"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O4" s="20"/>
     </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O5" s="20"/>
     </row>
-    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O6" s="20"/>
     </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7"/>
       <c r="O7" s="20"/>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" s="10" t="str">
         <f>IF(AND($C$102="Buyer",$I$18=1175),"Good job! You placed"," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10" t="str">
         <f>IF(AND($C$102="Buyer",$I$18=1175),"your first column field."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L11" s="10" t="str">
         <f>IF(AND($C$102="Buyer",$I$18=1175),"Click Next to continue..."," ")</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B100" s="11"/>
       <c r="C100" s="11" t="s">
         <v>2</v>
@@ -34644,7 +34666,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B101" s="11"/>
       <c r="C101" s="11" t="s">
         <v>4</v>
@@ -34662,7 +34684,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B102" s="11"/>
       <c r="C102" s="11" t="s">
         <v>5</v>
@@ -34680,7 +34702,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B103" s="11"/>
       <c r="C103" s="11" t="s">
         <v>6</v>
@@ -34698,7 +34720,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B104" s="11"/>
       <c r="C104" s="11" t="s">
         <v>7</v>
@@ -34716,7 +34738,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C105" s="7" t="s">
         <v>14</v>
       </c>
@@ -34733,11 +34755,11 @@
         <v>988</v>
       </c>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.35">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:7" x14ac:dyDescent="0.35">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34763,51 +34785,51 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52595332-3061-4A1A-A433-FAE60639EA6B}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="11.109375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="3" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="11.08984375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="13.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="11"/>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
@@ -34817,7 +34839,7 @@
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
     </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="11" t="s">
         <v>18</v>
       </c>
@@ -34827,7 +34849,7 @@
       <c r="H14" s="11"/>
       <c r="I14" s="11"/>
     </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="11" t="s">
         <v>18</v>
       </c>
@@ -34837,7 +34859,7 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
     </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="11" t="s">
         <v>18</v>
       </c>
@@ -34847,7 +34869,7 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
     </row>
-    <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="7" t="s">
         <v>19</v>
       </c>
@@ -34857,7 +34879,7 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
     </row>
-    <row r="18" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="7" t="s">
         <v>19</v>
       </c>
@@ -34867,103 +34889,103 @@
       <c r="H18" s="11"/>
       <c r="I18" s="11"/>
     </row>
-    <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H19" s="11"/>
       <c r="I19" s="11"/>
     </row>
-    <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H20" s="11"/>
       <c r="I20" s="11"/>
     </row>
-    <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H21" s="11"/>
       <c r="I21" s="11"/>
     </row>
-    <row r="22" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
     </row>
-    <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
     </row>
-    <row r="24" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
     </row>
-    <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H25" s="11"/>
       <c r="I25" s="11"/>
     </row>
-    <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="H26" s="11"/>
       <c r="I26" s="11"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
       <c r="H27" s="11"/>
       <c r="I27" s="11"/>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="H28" s="11"/>
       <c r="I28" s="11"/>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -34989,38 +35011,38 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C08892-693F-4163-9FFB-B7A94019F9E0}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:L106"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="11.109375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="3" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="11.08984375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.08984375" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21"/>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L11" s="10"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G13" s="23" t="s">
         <v>20</v>
       </c>
@@ -35031,7 +35053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G14" s="25"/>
       <c r="H14" s="25" t="s">
         <v>18</v>
@@ -35040,7 +35062,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G15" s="26"/>
       <c r="H15" s="26" t="s">
         <v>19</v>
@@ -35049,7 +35071,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G16" s="25"/>
       <c r="H16" s="27" t="s">
         <v>21</v>
@@ -35058,7 +35080,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G17" s="26"/>
       <c r="H17" s="28" t="s">
         <v>22</v>
@@ -35067,7 +35089,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G18" s="25"/>
       <c r="H18" s="25" t="s">
         <v>23</v>
@@ -35076,57 +35098,57 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B96" s="11"/>
       <c r="C96" s="11"/>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
       <c r="E99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
@@ -35150,40 +35172,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4871CEE6-57A7-4C76-B5A9-FF1C03A53814}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1:L107"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="11.109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.109375" style="7" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="3" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="11.08984375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.08984375" style="7" customWidth="1"/>
+    <col min="11" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G12" s="22" t="s">
         <v>25</v>
       </c>
@@ -35194,7 +35216,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G13" s="31">
         <v>43101</v>
       </c>
@@ -35205,7 +35227,7 @@
         <v>0.33754898404938316</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G14" s="31">
         <v>43102</v>
       </c>
@@ -35216,7 +35238,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G15" s="31">
         <v>43103</v>
       </c>
@@ -35227,7 +35249,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G16" s="31">
         <v>43104</v>
       </c>
@@ -35238,7 +35260,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G17" s="31">
         <v>43105</v>
       </c>
@@ -35249,7 +35271,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G18" s="31">
         <v>43106</v>
       </c>
@@ -35260,57 +35282,57 @@
         <v>0.23900536726791932</v>
       </c>
     </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
@@ -35335,40 +35357,40 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E34304-B7D8-4D3F-BF66-6C20E68C384F}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:L108"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.109375" style="6"/>
-    <col min="2" max="3" width="14.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="11.109375" style="7" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="7"/>
+    <col min="1" max="1" width="9.08984375" style="6"/>
+    <col min="2" max="3" width="14.90625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="11.08984375" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="9.08984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G12" s="34" t="s">
         <v>27</v>
       </c>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G13" s="22" t="s">
         <v>25</v>
       </c>
@@ -35379,7 +35401,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G14" s="35">
         <v>43101</v>
       </c>
@@ -35390,7 +35412,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G15" s="35">
         <v>43102</v>
       </c>
@@ -35401,7 +35423,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G16" s="35">
         <v>43103</v>
       </c>
@@ -35412,7 +35434,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G17" s="35">
         <v>43104</v>
       </c>
@@ -35423,7 +35445,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="7:9" x14ac:dyDescent="0.35">
       <c r="G18" s="35">
         <v>43105</v>
       </c>
@@ -35434,57 +35456,57 @@
         <v>900</v>
       </c>
     </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B98" s="11"/>
       <c r="C98" s="11"/>
     </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B99" s="11"/>
       <c r="C99" s="11"/>
     </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B100" s="11"/>
       <c r="C100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B101" s="11"/>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B102" s="11"/>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
       <c r="E102" s="11"/>
     </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
       <c r="E103" s="11"/>
     </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B104" s="11"/>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
       <c r="E104" s="11"/>
     </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B105" s="11"/>
       <c r="C105" s="11"/>
       <c r="D105" s="11"/>
       <c r="E105" s="11"/>
     </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D107" s="11"/>
       <c r="E107" s="11"/>
     </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:5" x14ac:dyDescent="0.35">
       <c r="D108" s="11"/>
       <c r="E108" s="11"/>
     </row>
